--- a/data/trans_dic/P6905-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6905-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,54; 37,21</t>
+          <t>19,45; 36,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,53; 28,27</t>
+          <t>8,38; 29,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,21; 33,27</t>
+          <t>10,71; 34,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 35,01</t>
+          <t>0,6; 35,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 38,02</t>
+          <t>10,47; 37,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,46; 46,51</t>
+          <t>16,34; 47,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,17; 67,5</t>
+          <t>22,07; 66,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,47; 75,98</t>
+          <t>23,22; 74,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,19; 34,38</t>
+          <t>19,42; 34,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,16; 31,53</t>
+          <t>14,92; 31,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,68; 38,61</t>
+          <t>16,98; 37,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,03; 46,97</t>
+          <t>12,91; 49,78</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,28; 35,48</t>
+          <t>24,19; 35,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,58; 35,59</t>
+          <t>23,03; 35,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,07; 32,57</t>
+          <t>20,45; 32,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,52; 26,74</t>
+          <t>15,84; 27,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,9; 57,76</t>
+          <t>37,79; 56,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,36; 51,5</t>
+          <t>33,41; 51,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,92; 53,55</t>
+          <t>36,11; 53,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,54; 34,11</t>
+          <t>16,51; 34,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,92; 39,6</t>
+          <t>30,28; 39,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,58; 39,5</t>
+          <t>29,1; 38,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,77; 37,88</t>
+          <t>27,54; 37,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,69; 28,26</t>
+          <t>18,78; 28,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,01; 48,01</t>
+          <t>25,21; 47,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,27; 37,77</t>
+          <t>13,33; 39,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,58; 47,83</t>
+          <t>22,41; 47,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,77; 51,48</t>
+          <t>22,08; 50,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,88; 52,54</t>
+          <t>26,32; 51,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,27; 61,54</t>
+          <t>29,83; 59,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,65; 48,76</t>
+          <t>25,5; 48,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,18; 51,45</t>
+          <t>33,03; 51,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,42; 45,8</t>
+          <t>29,17; 46,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,98; 47,34</t>
+          <t>26,45; 46,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,7; 44,06</t>
+          <t>26,92; 44,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,9; 47,62</t>
+          <t>31,37; 47,65</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,47; 34,65</t>
+          <t>26,21; 35,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,18; 31,08</t>
+          <t>21,41; 31,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,26; 32,56</t>
+          <t>21,76; 31,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,38; 28,67</t>
+          <t>17,85; 28,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,05; 47,36</t>
+          <t>34,53; 47,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,47; 48,33</t>
+          <t>33,72; 48,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,99; 48,37</t>
+          <t>34,46; 48,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,97; 38,4</t>
+          <t>23,83; 38,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,19; 37,43</t>
+          <t>29,6; 37,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,29; 36,29</t>
+          <t>28,05; 36,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,27; 36,8</t>
+          <t>28,64; 36,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,01; 31,82</t>
+          <t>22,07; 31,57</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21743; 41407</t>
+          <t>21642; 40788</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4832; 16021</t>
+          <t>4750; 16486</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6230; 18493</t>
+          <t>5954; 18967</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>173; 10227</t>
+          <t>175; 10359</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4049; 14285</t>
+          <t>3933; 13915</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6244; 17644</t>
+          <t>6198; 17854</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3995; 12166</t>
+          <t>3979; 11991</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5615; 18984</t>
+          <t>5801; 18721</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28563; 51172</t>
+          <t>28910; 51329</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13396; 29826</t>
+          <t>14118; 29788</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12278; 28416</t>
+          <t>12495; 27635</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6521; 25455</t>
+          <t>6995; 26981</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69675; 101804</t>
+          <t>69403; 101999</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50035; 78874</t>
+          <t>51029; 79112</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48323; 74713</t>
+          <t>46906; 73789</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37185; 64062</t>
+          <t>37956; 65368</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46125; 68487</t>
+          <t>44806; 66656</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43564; 67248</t>
+          <t>43624; 67380</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44744; 66699</t>
+          <t>44985; 66352</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39422; 81306</t>
+          <t>39354; 81408</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>121332; 160564</t>
+          <t>122791; 160636</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100654; 139113</t>
+          <t>102504; 136610</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>98309; 134089</t>
+          <t>97475; 132799</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>89324; 135057</t>
+          <t>89767; 136234</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19264; 35563</t>
+          <t>18674; 35100</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6117; 17408</t>
+          <t>6142; 18010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14346; 30383</t>
+          <t>14238; 29959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16529; 35791</t>
+          <t>15353; 34909</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17836; 33619</t>
+          <t>16839; 33195</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14020; 28508</t>
+          <t>13820; 27782</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18909; 35942</t>
+          <t>18795; 35730</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30094; 46667</t>
+          <t>29961; 47088</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40619; 63228</t>
+          <t>40270; 63964</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23083; 43749</t>
+          <t>24440; 43125</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36648; 60466</t>
+          <t>36938; 60883</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51107; 76302</t>
+          <t>50267; 76352</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>120280; 163652</t>
+          <t>123771; 166150</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68702; 100816</t>
+          <t>69460; 101574</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77573; 113483</t>
+          <t>75845; 109860</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>62190; 97009</t>
+          <t>60384; 96202</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>77154; 104241</t>
+          <t>76002; 104901</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74043; 103828</t>
+          <t>72440; 103677</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75682; 104613</t>
+          <t>74529; 104549</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84856; 135961</t>
+          <t>84380; 134923</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>209046; 259159</t>
+          <t>204964; 256786</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>152526; 195686</t>
+          <t>151276; 196280</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>159653; 207816</t>
+          <t>161740; 206875</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>159303; 220290</t>
+          <t>152827; 218611</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6905-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6905-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,45; 36,65</t>
+          <t>19,91; 37,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,38; 29,09</t>
+          <t>8,44; 29,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,71; 34,12</t>
+          <t>11,54; 34,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 35,46</t>
+          <t>3,2; 33,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,47; 37,04</t>
+          <t>10,73; 38,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 47,06</t>
+          <t>15,81; 44,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,07; 66,53</t>
+          <t>22,23; 66,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,22; 74,93</t>
+          <t>16,16; 46,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,42; 34,48</t>
+          <t>19,71; 34,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,92; 31,48</t>
+          <t>13,82; 31,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,98; 37,54</t>
+          <t>17,37; 38,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,91; 49,78</t>
+          <t>11,82; 32,57</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,19; 35,55</t>
+          <t>24,13; 35,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,03; 35,7</t>
+          <t>22,48; 34,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,45; 32,17</t>
+          <t>19,72; 32,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 27,28</t>
+          <t>16,61; 28,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,79; 56,22</t>
+          <t>38,57; 56,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,41; 51,6</t>
+          <t>34,05; 51,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,11; 53,27</t>
+          <t>35,57; 52,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,51; 34,15</t>
+          <t>25,75; 36,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,28; 39,61</t>
+          <t>30,53; 40,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,1; 38,79</t>
+          <t>28,68; 39,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,54; 37,52</t>
+          <t>27,6; 37,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,78; 28,5</t>
+          <t>22,22; 30,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,21; 47,38</t>
+          <t>24,29; 46,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,33; 39,08</t>
+          <t>13,35; 39,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,41; 47,16</t>
+          <t>21,94; 45,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,08; 50,21</t>
+          <t>29,08; 57,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,32; 51,88</t>
+          <t>27,05; 52,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,83; 59,98</t>
+          <t>31,72; 61,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,5; 48,47</t>
+          <t>24,73; 47,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,03; 51,92</t>
+          <t>32,84; 49,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,17; 46,33</t>
+          <t>29,46; 45,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,45; 46,67</t>
+          <t>25,88; 45,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,92; 44,36</t>
+          <t>27,21; 44,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,37; 47,65</t>
+          <t>33,8; 49,59</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,21; 35,18</t>
+          <t>25,66; 34,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,41; 31,31</t>
+          <t>21,34; 31,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,76; 31,52</t>
+          <t>22,19; 31,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,85; 28,44</t>
+          <t>19,88; 30,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,53; 47,66</t>
+          <t>34,12; 48,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,72; 48,26</t>
+          <t>33,92; 47,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,46; 48,34</t>
+          <t>34,96; 48,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,83; 38,11</t>
+          <t>29,19; 38,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,6; 37,08</t>
+          <t>29,8; 37,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,05; 36,4</t>
+          <t>27,91; 36,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,64; 36,63</t>
+          <t>28,28; 36,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,07; 31,57</t>
+          <t>25,92; 32,89</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13976</t>
+          <t>11999</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21642; 40788</t>
+          <t>22158; 42263</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4750; 16486</t>
+          <t>4781; 16689</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5954; 18967</t>
+          <t>6412; 19416</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>175; 10359</t>
+          <t>1160; 12208</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3933; 13915</t>
+          <t>4033; 14648</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6198; 17854</t>
+          <t>5997; 16713</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3979; 11991</t>
+          <t>4007; 12041</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5801; 18721</t>
+          <t>3959; 11285</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28910; 51329</t>
+          <t>29335; 51212</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14118; 29788</t>
+          <t>13079; 29367</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12495; 27635</t>
+          <t>12782; 28158</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6995; 26981</t>
+          <t>7180; 19775</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49738</t>
+          <t>59990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>65161</t>
+          <t>67997</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>114899</t>
+          <t>127988</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69403; 101999</t>
+          <t>69253; 102322</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51029; 79112</t>
+          <t>49813; 76722</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46906; 73789</t>
+          <t>45224; 74529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37956; 65368</t>
+          <t>44810; 76069</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44806; 66656</t>
+          <t>45729; 67382</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43624; 67380</t>
+          <t>44462; 67603</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44985; 66352</t>
+          <t>44312; 65329</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39354; 81408</t>
+          <t>56867; 80914</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>122791; 160636</t>
+          <t>123795; 162224</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>102504; 136610</t>
+          <t>101011; 138223</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97475; 132799</t>
+          <t>97677; 132006</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>89767; 136234</t>
+          <t>109033; 149123</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>32407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38050</t>
+          <t>40704</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63083</t>
+          <t>73111</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18674; 35100</t>
+          <t>17990; 34745</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6142; 18010</t>
+          <t>6154; 18277</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14238; 29959</t>
+          <t>13938; 29211</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15353; 34909</t>
+          <t>22615; 45008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16839; 33195</t>
+          <t>17306; 33490</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13820; 27782</t>
+          <t>14693; 28343</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18795; 35730</t>
+          <t>18226; 35195</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29961; 47088</t>
+          <t>32651; 49513</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40270; 63964</t>
+          <t>40669; 63005</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24440; 43125</t>
+          <t>23920; 41897</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36938; 60883</t>
+          <t>37337; 61561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50267; 76352</t>
+          <t>59876; 87857</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77548</t>
+          <t>97134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>114409</t>
+          <t>115964</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>191958</t>
+          <t>213098</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>123771; 166150</t>
+          <t>121184; 162733</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69460; 101574</t>
+          <t>69235; 101153</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75845; 109860</t>
+          <t>77317; 110979</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60384; 96202</t>
+          <t>76275; 116714</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76002; 104901</t>
+          <t>75100; 105759</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72440; 103677</t>
+          <t>72880; 103075</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>74529; 104549</t>
+          <t>75610; 105648</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84380; 134923</t>
+          <t>100628; 131269</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>204964; 256786</t>
+          <t>206311; 256365</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>151276; 196280</t>
+          <t>150479; 196858</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>161740; 206875</t>
+          <t>159716; 205786</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>152827; 218611</t>
+          <t>188854; 239573</t>
         </is>
       </c>
     </row>
